--- a/artfynd/A 35705-2025 artfynd.xlsx
+++ b/artfynd/A 35705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781003</v>
       </c>
       <c r="B2" t="n">
-        <v>91751</v>
+        <v>91757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35705-2025 artfynd.xlsx
+++ b/artfynd/A 35705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781003</v>
       </c>
       <c r="B2" t="n">
-        <v>91757</v>
+        <v>91760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127781041</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127781061</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35705-2025 artfynd.xlsx
+++ b/artfynd/A 35705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781003</v>
       </c>
       <c r="B2" t="n">
-        <v>91760</v>
+        <v>91768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127781041</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127781061</v>
       </c>
       <c r="B4" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35705-2025 artfynd.xlsx
+++ b/artfynd/A 35705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781003</v>
       </c>
       <c r="B2" t="n">
-        <v>91768</v>
+        <v>91769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35705-2025 artfynd.xlsx
+++ b/artfynd/A 35705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781003</v>
       </c>
       <c r="B2" t="n">
-        <v>91771</v>
+        <v>91779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127781041</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127781061</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35705-2025 artfynd.xlsx
+++ b/artfynd/A 35705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781003</v>
       </c>
       <c r="B2" t="n">
-        <v>91779</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127781041</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127781061</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
